--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>67.81910355438902</v>
+        <v>11.02060432758821</v>
       </c>
       <c r="D2" t="n">
-        <v>68.00965877331923</v>
+        <v>11.05156955066438</v>
       </c>
       <c r="E2" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F2" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.32416750685124</v>
+        <v>12.56517721986333</v>
       </c>
       <c r="D3" t="n">
-        <v>77.39199507092253</v>
+        <v>12.57619919902491</v>
       </c>
       <c r="E3" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F3" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.79628202886948</v>
+        <v>8.254395829691292</v>
       </c>
       <c r="D4" t="n">
-        <v>51.17436027556489</v>
+        <v>8.315833544779295</v>
       </c>
       <c r="E4" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F4" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.4453913575652</v>
+        <v>11.44737609560435</v>
       </c>
       <c r="D5" t="n">
-        <v>70.44044947237427</v>
+        <v>11.44657303926082</v>
       </c>
       <c r="E5" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F5" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.97948054459844</v>
+        <v>9.259165588497247</v>
       </c>
       <c r="D6" t="n">
-        <v>57.58486500262739</v>
+        <v>9.357540562926951</v>
       </c>
       <c r="E6" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F6" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.65442930811201</v>
+        <v>6.768844762568201</v>
       </c>
       <c r="D7" t="n">
-        <v>42.00634968665646</v>
+        <v>6.826031824081674</v>
       </c>
       <c r="E7" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F7" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.559318824216659</v>
+        <v>0.9033893089352071</v>
       </c>
       <c r="D8" t="n">
-        <v>5.337918625315232</v>
+        <v>0.8674117766137251</v>
       </c>
       <c r="E8" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F8" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.54579176291214</v>
+        <v>6.101191161473222</v>
       </c>
       <c r="D9" t="n">
-        <v>37.04322898080345</v>
+        <v>6.01952470938056</v>
       </c>
       <c r="E9" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F9" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.95975475480533</v>
+        <v>6.655960147655867</v>
       </c>
       <c r="D10" t="n">
-        <v>40.36003416028795</v>
+        <v>6.558505551046792</v>
       </c>
       <c r="E10" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F10" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>67.00967295616155</v>
+        <v>10.88907185537625</v>
       </c>
       <c r="D11" t="n">
-        <v>66.52427934209675</v>
+        <v>10.81019539309072</v>
       </c>
       <c r="E11" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F11" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>92.35236551546049</v>
+        <v>15.00725939626233</v>
       </c>
       <c r="D12" t="n">
-        <v>92.1595729822688</v>
+        <v>14.97593060961868</v>
       </c>
       <c r="E12" t="n">
-        <v>22.53373778621696</v>
+        <v>3.661732390260257</v>
       </c>
       <c r="F12" t="n">
-        <v>22.59347340890642</v>
+        <v>3.671439428947294</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
